--- a/data/raw/rdr2_patch.xlsx
+++ b/data/raw/rdr2_patch.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="animals" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ingredient_animals" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="animals" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ingredient_animals" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="recipes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -58,7 +59,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -73,6 +74,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5242,4 +5244,70 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" style="7" min="1" max="1"/>
+    <col width="32" customWidth="1" style="7" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>recipe-explosive-slug</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Explosive Shotgun Slug</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>recipe-incendiary-buckshot</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Buckshot Incendiary Shotgun Shell</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>recipe-plain-big-game-meat</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Plain Big Game</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/raw/rdr2_patch.xlsx
+++ b/data/raw/rdr2_patch.xlsx
@@ -6,6 +6,8 @@
     <sheet name="animals" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="ingredient_animals" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="recipes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="plants" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ingredient_plants" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -353,6 +355,8 @@
   <dimension ref="A1:Z96"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
+    <col width="13" customWidth="1" style="7" min="1" max="1"/>
+    <col width="13" customWidth="1" style="7" min="2" max="2"/>
     <col width="23" customWidth="1" style="7" min="3" max="3"/>
     <col width="16.5" customWidth="1" style="7" min="4" max="4"/>
     <col width="35.75" customWidth="1" style="7" min="5" max="5"/>
@@ -5310,4 +5314,863 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" style="7" min="1" max="1"/>
+    <col width="13" customWidth="1" style="7" min="2" max="2"/>
+    <col width="23" customWidth="1" style="7" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>plant-alaskan-ginseng</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Alaskan Ginseng</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>plant-american-ginseng</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>American Ginseng</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>plant-bay-bolete</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bay Bolete</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>plant-beet</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Beet</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>plant-blackberry</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Blackberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>plant-blackcurrant</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Blackcurrant</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>plant-burdock-root</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Burdock Root</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>plant-chanterelle</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Chanterelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>plant-common-bulrush</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Common Bulrush</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>plant-creeping-thyme</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Creeping Thyme</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>plant-desert-sage</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Desert Sage</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>plant-english-mace</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>English Mace</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>plant-evergreen-huckleberry</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Evergreen Huckleberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>plant-golden-currant</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Golden Currant</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>plant-ground-coffee</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ground Coffee</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>plant-hay</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Hay</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>plant-hummingbird-sage</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Hummingbird Sage</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>plant-indian-tobacco</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Indian Tobacco</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>plant-milkweed</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Milkweed</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>plant-oleander-sage</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Oleander Sage</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>plant-oregano</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Oregano</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>plant-parasol-mushroom</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Parasol Mushroom</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>plant-prairie-poppy</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Prairie Poppy</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>plant-ram-s-head</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ram's Head</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>plant-raspberry</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Raspberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>plant-red-sage</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Red Sage</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>plant-vanilla-flower</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Vanilla Flower</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>plant-violet-snowdrop</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Violet Snowdrop</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>plant-wild-carrot</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Wild Carrot</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>plant-wild-feverfew</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Wild Feverfew</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>plant-wild-mint</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Wild Mint</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>plant-wintergreen-berry</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Wintergreen Berry</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>plant-yarrow</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Yarrow</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" style="7" min="1" max="1"/>
+    <col width="13" customWidth="1" style="7" min="2" max="2"/>
+    <col width="23" customWidth="1" style="7" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>ingredient_id</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>plant_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ing-bay-bolete</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>plant-bay-bolete</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ing-beet</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>plant-beet</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ing-blackberry</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>plant-blackberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ing-burdock-root</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>plant-burdock-root</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ing-chanterelle</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>plant-chanterelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ing-common-bulrush</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>plant-common-bulrush</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ing-creeping-thyme</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>plant-creeping-thyme</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ing-currant</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>plant-blackcurrant</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ing-currant</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>plant-golden-currant</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ing-english-mace</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>plant-english-mace</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ing-evergreen-huckleberry</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>plant-evergreen-huckleberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ing-ginseng</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>plant-alaskan-ginseng</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ing-ginseng</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>plant-american-ginseng</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ing-ground-coffee</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>plant-ground-coffee</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ing-hay</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>plant-hay</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ing-indian-tobacco</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>plant-indian-tobacco</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ing-milkweed</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>plant-milkweed</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ing-oleander-sage</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>plant-oleander-sage</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ing-oregano</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>plant-oregano</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ing-parasol-mushroom</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>plant-parasol-mushroom</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ing-prairie-poppy</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>plant-prairie-poppy</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ing-ram-s-head</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>plant-ram-s-head</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ing-raspberry</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>plant-raspberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ing-sage</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>plant-desert-sage</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ing-sage</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>plant-hummingbird-sage</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ing-sage</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>plant-red-sage</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ing-vanilla-flower</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>plant-vanilla-flower</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ing-violet-snowdrop</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>plant-violet-snowdrop</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ing-wild-carrot</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>plant-wild-carrot</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ing-wild-feverfew</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>plant-wild-feverfew</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ing-wild-mint</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>plant-wild-mint</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ing-wintergreen-berry</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>plant-wintergreen-berry</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ing-yarrow</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>plant-yarrow</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>